--- a/data/input/cnv_data.xlsx
+++ b/data/input/cnv_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\alexandra\cnv-data\data\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\alexandra\chapter1\cnv-data\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CF571D-4BCC-409D-A448-5F7A5F2993DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9224E83-3390-4902-B2A6-48D22785BFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cnv_input_table" sheetId="1" r:id="rId1"/>
@@ -2351,7 +2351,7 @@
         <v>38</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>38</v>
@@ -2378,7 +2378,7 @@
         <v>10</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>10</v>

--- a/data/input/cnv_data.xlsx
+++ b/data/input/cnv_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\alexandra\chapter1\cnv-data\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9224E83-3390-4902-B2A6-48D22785BFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18BEB60-895C-4782-86EF-96DDB598D90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="283">
   <si>
     <t xml:space="preserve">in my retrieved gene, but not in the wikipathways </t>
   </si>
@@ -596,9 +596,6 @@
     <t>1q21.1</t>
   </si>
   <si>
-    <t>The distal 1q21.1 copy number variation syndrome can result in the loss or duplication of up to 20 protein-coding genes.</t>
-  </si>
-  <si>
     <t>Chr1:145394955-145807817</t>
   </si>
   <si>
@@ -611,9 +608,6 @@
     <t>1q21.1-q21.2</t>
   </si>
   <si>
-    <t>The distal 1q21.1-q21.2 copy number variation syndrome can result in the loss or duplication of up to 7 protein-coding genes, leading to widespread effects on human development.</t>
-  </si>
-  <si>
     <t>Chr1:146527987-147394444</t>
   </si>
   <si>
@@ -735,9 +729,6 @@
   </si>
   <si>
     <t>16p13.11</t>
-  </si>
-  <si>
-    <t>Copy number variations in the region 16p13.11 are risks for neuropsychiatric diseases like schizophrenia.</t>
   </si>
   <si>
     <t>Chr16:15511655-16293689</t>
@@ -1657,6 +1648,99 @@
     <t>• Missing PRAG1 gene
 • Has an extra RNA, long non-coding, C8orf12. 
 • C8orf49 changed name into LINC02905. But it's not a protein codin gene.</t>
+  </si>
+  <si>
+    <t>3320(deletion)</t>
+  </si>
+  <si>
+    <t>The TAR syndrome (Thrombocytopenia with Absent Radius) is a rare genetic disorder caused by a deletion on the chromosome 1 (GRCh37: chr1:145,394,955-145,807,817 according to Kirov et al. 2014 10.1016/j.biopsych.2013.07.022). The most notable symptoms are the absence of the radius bone, reduced platelet count and cardiac defects. Additionally, patients have an increased susceptibility for psychiatric disorders.</t>
+  </si>
+  <si>
+    <t>1q21.1 copy number variation (deletion or duplication)  can result in the loss or duplication of up to 7 protein-coding genes, leading to widespread effects on human development. The syndromes are known for a highly variable phenotype especially concerning psychiatric problems. The breakpoints (chr1:146,527,987-147,394,444, GRCh37/hg19) are defined as given in Kendall et al. 2017: https://doi.org/10.1016/j.biopsych.2016.08.014.</t>
+  </si>
+  <si>
+    <t>The 2q11.2 copy number variation syndrome can result in the loss of up to 27 protein-coding genes. Patients with 2q11.2 deletions were reported to have developmental delay, speech delay and ADHD, while subjects with 2q11.2 duplications apart from developmental delay had gastroesophageal reflux and short stature (DOI: 10.1002/ajmg.a.37269).</t>
+  </si>
+  <si>
+    <t>Mutations or loss of NPHP1 cause nephronophthisis (NPHP), a rare genetic disorder. Due to the involvement of NPHP1 in ciliary function and cellular orientation in kidney, the main symptoms of the disorder are found in kidney development and function. However, as in many ciliopathies, neuronal functions are also affected, causing psychiatric disorders.</t>
+  </si>
+  <si>
+    <t>The 2q13 copy number variation syndrome can result in the loss of up to 25 protein-coding genes. Patients with 2q13 deletions and duplications had abnormal head size and dysmorphic features (DOI: 10.1002/ajmg.a.37269). 2q13 duplications also caused developmental delay. The abnormal head size in 2q13 could be explained by the changes in FBLN7 gene (DOI: 10.1002/ajmg.a.37269). At the same time, neuropsychiatric impairment in 2q13 may be associated with BCL2L11, ANAPC1, SLC1A1 and MERTK alterations (DOI: 10.1002/ajmg.b.32236).</t>
+  </si>
+  <si>
+    <t>10q11.21q11.23 copy number variation (CNV) syndrome is a rare genetic disorder caused by a deletion or duplication of genetic material on chromosome 10. The exact genetic location chr10:49,390,199-51,058,796 (GRCh37) was taken from Kirov et al. 2014</t>
+  </si>
+  <si>
+    <t>10q22q23 copy number variation syndrome is a rare genetic syndrome caused by a deletion or duplication in the region 10q22q23 of chromosome 10. The exact position (chr10:82,045,472-88,931,651, GRCh37) was taken from Kirov et al. 2014. Patients usually suffer from developmental delay and psychiatric disorders as well as facial dyspmorphisms, and cardiac abnormalities.</t>
+  </si>
+  <si>
+    <t>A deletion in 11p11.2 can cause the Potocki-Shaffer syndrome (MIM # 601224) which is characterised by malformations in the heart, kidney and urinary tract.</t>
+  </si>
+  <si>
+    <t>Deletion or duplication of the CRYL1 gene located at chromosome 13q12 (chr13:20977806-21100012 (GRCh37)) is a risk factor for psychiatric disorders (Kirov et al. 2014).</t>
+  </si>
+  <si>
+    <t>Copy number variations in the region 13q12.12 (exact position: chr13:23555358-24884622 (GRCh37), numbers from Kirov et al. 2014 10.1016/j.biopsych.2013.07.022 ) are rare, pathological mutations in the human genome. It is a risk variation for neuropsychiatric diseases like schizophrenia (Kirov et al. 2014, 10.1016/j.biopsych.2013.07.022) and with the presence of SACS it harbors a gene known for causing Spastic ataxia (MIM # 270550).</t>
+  </si>
+  <si>
+    <t>The 15q11.2 deletion or duplication syndromes, also known as Burnside-Butler syndrome (BBS). This region is relatively small compared to other CNVs but it contains NIPA1 and NIPA2, two important magnesium transporters, which are active in the central nervous system. CYFIP1 is an important interactor with FMR1, which is the causative gene for fragile X syndrome. The breakpoints (chr15:22,805,313-23,094,530 GRCh37/hg19) are defined as given in Kendall et al. 2017: https://doi.org/10.1016/j.biopsych.2016.08.014.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prader-Willi syndrome (PWS) and Angelman syndrome (AS) are diseases that are both caused by a deletion in the same region of chromosome 15, namely 15q11-q13 (exact position chr15:22805313-28390339 (GRCh37) taken from Kirov et al. 2014). Due to methylation patterns however, different genes are responsible for the two syndromes. For this chromosomal region, also duplications are known.  A detailed description of the syndromes in this region and the molecular pathway has been published by Ehrhart et al. (https://doi.org/10.1080/15622975.2018.1439594). </t>
+  </si>
+  <si>
+    <t>The major genes in this region are OTUD7A and CHRNA7 which are known influencers of neuronal development and function. For several genes in this regio there are no exact functions known yet - e.g. the GOLGA gene group or the MTMR10 which is similar to phosphatidyl-inositol 3 phosphatases but without an active catalytic centre. The breakpoints 30,500,000-32,500,000 are from “15q13.3 Microdeletion”, Bregje WM van Bon et al. in Gene reviews PMID: 20301295.</t>
+  </si>
+  <si>
+    <t> 15q25 copy number variations are rare genetic disorders that cause neuropsychiatric disorders, developmental delay and cardiac abnormalities. The exact chromosomal position for this pathway (chr15:83219735-85722039, GRCh37) was taken from Kirov et al. 2014 10.1016/j.biopsych.2013.07.022.</t>
+  </si>
+  <si>
+    <t>16p11.2 distal deletion syndrome is a rare genetic disorder (copy number variation) caused by a deletion on chromosome 16 in the range 28.74-28.95-Mb. The breakpoints in this pathway are chr16:28,823,196-29,046,783 (GHCh37) from Kendall et al. 2017 https://doi.org/10.1016/j.biopsych.2016.08.014.</t>
+  </si>
+  <si>
+    <t>16p11.2 proximal deletion syndrome is a rare genetic disorder (copy number variation) caused by a deletion in the region of chromosome 16 from 29,592,751 to 30,190,593 bp (GRCh37). The breakpoints are from: Dell’Edera 2018 PMID: 29609622.</t>
+  </si>
+  <si>
+    <t>Copy number variations in the region 16p12.2 are rare, pathological mutations in the human genome. It is a risk variation for neuropsychiatric diseases like schizophrenia (Kirov et al. 2014, 10.1016/j.biopsych.2013.07.022)</t>
+  </si>
+  <si>
+    <t>Copy number variations in the region 16p13.11 are risks for neuropsychiatric diseases like schizophrenia (Kirov et al. 2014, 10.1016/j.biopsych.2013.07.022).</t>
+  </si>
+  <si>
+    <t>The 17p13.3 deletion or duplication ranging from chr17:1250000 to chr17:1300000, affects YWHAE gene. The YWHAE gene plays a role in a lot of different processes and is closely related to many diseases.</t>
+  </si>
+  <si>
+    <t>The NF1 deletion and NF1 duplication, ranging from chr17: 29,100,000 to chr17: 30,280,000 can result in a loss of up to 14 protein coding genes, including NF1.</t>
+  </si>
+  <si>
+    <t>The 2q21.1 copy number variation syndrome can result in the loss of up to 9 protein-coding genes. Deletions and duplications in 2q21.1 were reported to be connected to intellectual disability, hyperactivity, and aggressive behavior (DOI: 10.1002/mgg3.1135,DOI: 10.1002/ajmg.a.36357). The clinical picture was explained by alterations in five genes important for neurological development, namely GPR148, FAM123C, ARHGEF4, FAM168B and PLEKHB2 (DOI: 10.1002/ajmg.a.36357,DOI: 10.1093/hmg/dds166). Analogically, changes in tubulin genes in 2q21.1 were linked to Motor Timing in ADHD (DOI: 10.1016/j.ajhg.2008.06.006). For this rare disorder, two different genomic locations are known according to Kirov et al. 2014, and Gimelli et al. 2014 with a larger deletion.</t>
+  </si>
+  <si>
+    <t>The 2q37 copy number variation syndrome can result in the loss of up to 78 protein-coding genes. Patients with 2q37 CNV syndrome have intellectual disability, facial dysmorphism and skeletal and digit malformations (DOI: 10.1186/1755-8794-7-19, DOI: 10.1016/j.gene.2013.06.056). Research linked changes in HDAC4 gene with obesity of 2q37 patients (DOI: 10.1016/j.gene.2013.06.056). Chromosomal locations are from Kirov et al. 2014 (chr2:239,716,679-243,199,373) and the larger one from Sakai et al. 2014 (chr2:234,275,216-243,199,373).</t>
+  </si>
+  <si>
+    <t>The Wolf-Hirschhorn syndrome is a rare genetic disorder caused by a microdeletion in the chromosomal region 4p16.3. Typical symptoms are a distinct facial morphology, intellectual disability, psychiatric disorders, seizures, and heart defects. The chromosomal position chr4:1,552,030-2,091,303 (GCRh37) was taken from Kirov et al. 2014 (10.1016/j.biopsych.2013.07.022).</t>
+  </si>
+  <si>
+    <t>A deletion in the chromosomal region 5q35 can cause the rare genetic disorder Sotos syndrome. Sotos syndrome is characterised by psychiatric disorders (autism, intellectual disability, developmental delay) and excessive growth. Also, duplication of 5q35 has been recorded.</t>
+  </si>
+  <si>
+    <t>7q11.23 copy number variation syndrome (MIM 609757, also called Williams-Beuren region duplication syndrome, WBS duplication syndrome, Chromosome 7q11.23 duplication syndrome, or Somerville-van-der-Aa syndrome) is a copy number variation syndrome with a duplication in the region chr7:72,744,454-74,142,513 (GRCh37/hg19). The breakpoint is defined from Carolyn B Mervis 7q11.23 Duplication Syndrome in Gene Reviews PMID: 20301295.</t>
+  </si>
+  <si>
+    <t>Deletion or duplication of the region chr7:75,138,294-76,064,412, also known as 7q11.23 distal (OMIM # 613729), are rare genetic disorders and can cause different neurological and neuropsychiatric symptoms. Patients are often observed with epilepsy and neurodevelopmental delay.</t>
+  </si>
+  <si>
+    <t>RB1CC1, located on chromosome 8q11.23, is mainly involved in autophagy regulation. A loss of function or mutation in the gene can result in increased risk for schizophrenia (Degenhardt et al. 2013).</t>
+  </si>
+  <si>
+    <t>Patients with a deletion often suffer from diaphragmatic hernia (CDH) and cardiac defects.</t>
+  </si>
+  <si>
+    <t>PAFAH1B1 located on chromosome 17p13.3 (exact position chr17:2496923-2588909, GRCh37, position from Kirov et al. 2014 10.1016/j.biopsych.2013.07.022) is responsible for the rare genetic disorder Miller-Dieker syndrome (MIM # 247200). The most common symptom is lisencephaly causing severe intellectual disability, cardiac and facial dysmorphic features. The protein is part of the type I platelet-activating factor acetylhydrolase and involved in stabilising dynein binding to microtubules.</t>
+  </si>
+  <si>
+    <t>The Smith-Magenis syndrome, is the result from a deletion of chr17:chr17:16,82-18,28, while the Potocki-Lupski syndrome is the result of a duplication of this area.</t>
   </si>
 </sst>
 </file>
@@ -1861,7 +1945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1890,9 +1974,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1901,12 +1982,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1946,6 +2021,35 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2255,25 +2359,25 @@
   <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.88671875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="14" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="14" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.88671875" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="41.109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.88671875" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="41.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.88671875" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>66</v>
@@ -2282,10 +2386,10 @@
         <v>67</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>68</v>
@@ -2294,911 +2398,1017 @@
         <v>4</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="138" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="8"/>
+        <v>83</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="F2" s="29"/>
       <c r="G2" s="8" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>246</v>
+        <v>207</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>73</v>
+        <v>81</v>
+      </c>
+      <c r="J2" s="34" t="s">
+        <v>81</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>247</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" s="8"/>
+        <v>86</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="F3" s="29"/>
       <c r="G3" s="8" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
+      </c>
+      <c r="J3" s="34" t="s">
+        <v>81</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="F4" s="8"/>
+        <v>90</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="F4" s="29"/>
       <c r="G4" s="8" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>10</v>
+        <v>208</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>85</v>
+        <v>94</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>261</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>88</v>
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
+        <v>262</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>92</v>
+        <v>100</v>
+      </c>
+      <c r="E7" t="s">
+        <v>263</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>211</v>
+        <v>101</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>16</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>34</v>
+        <v>102</v>
+      </c>
+      <c r="K7" s="31" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>53</v>
+        <v>109</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" t="s">
+        <v>264</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>83</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="J8" s="35"/>
       <c r="K8" s="9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>99</v>
+        <v>113</v>
+      </c>
+      <c r="E9" t="s">
+        <v>265</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>83</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="J9" s="35"/>
       <c r="K9" s="9" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>102</v>
+        <v>117</v>
+      </c>
+      <c r="E10" t="s">
+        <v>266</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>16</v>
+        <v>118</v>
+      </c>
+      <c r="H10" s="32" t="s">
+        <v>59</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>16</v>
+        <v>81</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" s="32" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" s="8"/>
+        <v>129</v>
+      </c>
+      <c r="D11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>267</v>
+      </c>
+      <c r="F11" s="29"/>
       <c r="G11" s="8" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>111</v>
+        <v>129</v>
+      </c>
+      <c r="D12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" t="s">
+        <v>268</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>115</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="F13" s="28"/>
       <c r="G13" s="8" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>117</v>
+        <v>127</v>
+      </c>
+      <c r="J13" s="34" t="s">
+        <v>81</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>119</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="F14" s="28"/>
       <c r="G14" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>83</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="J14" s="35"/>
       <c r="K14" s="9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15" s="8"/>
+        <v>138</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="F15" s="29"/>
       <c r="G15" s="8" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>129</v>
+      <c r="A16" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="I16" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="160.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D17" t="s">
-        <v>133</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="28"/>
       <c r="G17" s="8" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>22</v>
+        <v>243</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>22</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D18" t="s">
-        <v>137</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="F18" s="28"/>
       <c r="G18" s="8" t="s">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="D19" s="29"/>
+      <c r="E19" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="F19" s="28"/>
       <c r="G19" s="8" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>44</v>
+        <v>215</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>145</v>
+        <v>171</v>
+      </c>
+      <c r="E20" t="s">
+        <v>255</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>235</v>
+        <v>24</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>251</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>61</v>
+        <v>159</v>
+      </c>
+      <c r="D21" s="29"/>
+      <c r="E21" t="s">
+        <v>257</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>150</v>
+        <v>81</v>
+      </c>
+      <c r="J21" s="34" t="s">
+        <v>81</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>152</v>
+        <v>164</v>
+      </c>
+      <c r="E22" t="s">
+        <v>273</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>42</v>
+        <v>211</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>154</v>
+        <v>81</v>
+      </c>
+      <c r="J22" s="34" t="s">
+        <v>81</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15" t="s">
-        <v>159</v>
+      <c r="A23" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="F23" s="30"/>
+      <c r="G23" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="J23" s="36"/>
+      <c r="K23" s="32" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>49</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="D24" s="29"/>
+      <c r="E24" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="F24" s="28"/>
       <c r="G24" s="8" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>83</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="J24" s="35"/>
       <c r="K24" s="9" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>162</v>
+        <v>184</v>
+      </c>
+      <c r="E25" t="s">
+        <v>275</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>83</v>
+        <v>186</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>167</v>
+        <v>188</v>
+      </c>
+      <c r="E26" t="s">
+        <v>276</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>214</v>
+        <v>46</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>83</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="J26" s="35"/>
       <c r="K26" s="9" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="146.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>170</v>
+        <v>192</v>
+      </c>
+      <c r="E27" t="s">
+        <v>277</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>248</v>
+        <v>14</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>250</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>23</v>
+        <v>195</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>174</v>
+        <v>192</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" t="s">
+        <v>278</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>24</v>
+        <v>237</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>24</v>
+        <v>198</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="F29" s="8"/>
+        <v>203</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>280</v>
+      </c>
+      <c r="F29" s="29"/>
       <c r="G29" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>218</v>
+        <v>204</v>
+      </c>
+      <c r="H29" s="25" t="s">
+        <v>250</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>8</v>
+        <v>205</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="F30" s="8"/>
+        <v>200</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="F30" s="29"/>
       <c r="G30" s="8" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>185</v>
+        <v>81</v>
+      </c>
+      <c r="J30" s="34" t="s">
+        <v>81</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>187</v>
+        <v>149</v>
+      </c>
+      <c r="E31" t="s">
+        <v>272</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>83</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="J31" s="35"/>
       <c r="K31" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>191</v>
+        <v>159</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" t="s">
+        <v>256</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>193</v>
+        <v>81</v>
+      </c>
+      <c r="J32" s="34" t="s">
+        <v>81</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>194</v>
+        <v>145</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>195</v>
+        <v>138</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" t="s">
+        <v>281</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>197</v>
+        <v>147</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>198</v>
+        <v>5</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>133</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D34" s="29"/>
+      <c r="E34" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" s="28"/>
       <c r="G34" s="8" t="s">
-        <v>200</v>
+        <v>106</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="K34" s="12" t="s">
-        <v>241</v>
+        <v>107</v>
+      </c>
+      <c r="K34" s="34" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>203</v>
+        <v>142</v>
+      </c>
+      <c r="E35" t="s">
+        <v>282</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>63</v>
+        <v>232</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>83</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="J35" s="35"/>
       <c r="K35" s="9" t="s">
-        <v>63</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>205</v>
+        <v>74</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>206</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="F36" s="28"/>
       <c r="G36" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="H36" s="28" t="s">
-        <v>253</v>
+        <v>76</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="K36" s="16" t="s">
-        <v>245</v>
+        <v>252</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K36" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K36" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K36">
+      <sortCondition ref="A1:A36"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3216,18 +3426,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3264,557 +3474,557 @@
   <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.88671875" style="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" style="26" customWidth="1"/>
-    <col min="3" max="4" width="40.88671875" style="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" style="26" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="26"/>
+    <col min="1" max="1" width="34.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" style="23" customWidth="1"/>
+    <col min="3" max="4" width="40.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" style="23" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="C1" s="18" t="s">
+      <c r="A1" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="E1" s="27" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="20" t="s">
+      <c r="D11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D27" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="E2" s="24" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="24" t="s">
+      <c r="E27" s="23" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="21" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="26" t="s">
+    <row r="30" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="D34" s="17" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="B34" s="19" t="s">
+      <c r="E34" s="23" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="C34" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="19" t="s">
+      <c r="C35" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="C35" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="D36" s="25" t="s">
+      <c r="C36" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="D36" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E36" s="24" t="s">
-        <v>254</v>
+      <c r="E36" s="21" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/cnv_data.xlsx
+++ b/data/input/cnv_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\alexandra\chapter1\cnv-data\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18BEB60-895C-4782-86EF-96DDB598D90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5178E8B6-81BB-4434-907E-322BC1829FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cnv_input_table" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="observations" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cnv_input_table!$A$1:$K$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cnv_input_table!$A$1:$L$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="381">
   <si>
     <t xml:space="preserve">in my retrieved gene, but not in the wikipathways </t>
   </si>
@@ -194,9 +194,6 @@
     <t>2q13 copy number variation syndrome</t>
   </si>
   <si>
-    <t>BUB1,ACOXL,BCL2L11</t>
-  </si>
-  <si>
     <t>2q21.1 copy number variation syndrome</t>
   </si>
   <si>
@@ -572,18 +569,12 @@
     <t>extra</t>
   </si>
   <si>
-    <t>region</t>
-  </si>
-  <si>
     <t>WP5345</t>
   </si>
   <si>
     <t>1p36.33-p36.32</t>
   </si>
   <si>
-    <t>1p36.33-p36.32 deletion or duplication syndromes are a rare genetic disorders caused by a deletion or duplication of the most distal light band of the short arm of chromosome 1.</t>
-  </si>
-  <si>
     <t>Chr1:0-2500000</t>
   </si>
   <si>
@@ -689,9 +680,6 @@
     <t>Chr15:22805313-28390339</t>
   </si>
   <si>
-    <t>739(deletion),72(deletion),261183(microdeletion),238446(microduplication),3306(inverted duplication)</t>
-  </si>
-  <si>
     <t>WP5407</t>
   </si>
   <si>
@@ -854,9 +842,6 @@
     <t>WP5222</t>
   </si>
   <si>
-    <t>Chr2:111394040-112012649</t>
-  </si>
-  <si>
     <t>WP5223</t>
   </si>
   <si>
@@ -957,9 +942,6 @@
   </si>
   <si>
     <t>WP5401</t>
-  </si>
-  <si>
-    <t>chr7:75138294-76064412</t>
   </si>
   <si>
     <t>254351(distal microdeletion),261102(distal microduplication)</t>
@@ -1287,9 +1269,6 @@
     </r>
   </si>
   <si>
-    <t>The pathway in WikiPathways is incorrect (wrong coordinates). Needs correction.</t>
-  </si>
-  <si>
     <t>• Missing SMIM39 gene that is in hg38, but not in hg19. In Wikipatwhays the coordinates are wornh. It should stop at the first line with PLEKHB2 gene</t>
   </si>
   <si>
@@ -1653,9 +1632,6 @@
     <t>3320(deletion)</t>
   </si>
   <si>
-    <t>The TAR syndrome (Thrombocytopenia with Absent Radius) is a rare genetic disorder caused by a deletion on the chromosome 1 (GRCh37: chr1:145,394,955-145,807,817 according to Kirov et al. 2014 10.1016/j.biopsych.2013.07.022). The most notable symptoms are the absence of the radius bone, reduced platelet count and cardiac defects. Additionally, patients have an increased susceptibility for psychiatric disorders.</t>
-  </si>
-  <si>
     <t>1q21.1 copy number variation (deletion or duplication)  can result in the loss or duplication of up to 7 protein-coding genes, leading to widespread effects on human development. The syndromes are known for a highly variable phenotype especially concerning psychiatric problems. The breakpoints (chr1:146,527,987-147,394,444, GRCh37/hg19) are defined as given in Kendall et al. 2017: https://doi.org/10.1016/j.biopsych.2016.08.014.</t>
   </si>
   <si>
@@ -1665,82 +1641,400 @@
     <t>Mutations or loss of NPHP1 cause nephronophthisis (NPHP), a rare genetic disorder. Due to the involvement of NPHP1 in ciliary function and cellular orientation in kidney, the main symptoms of the disorder are found in kidney development and function. However, as in many ciliopathies, neuronal functions are also affected, causing psychiatric disorders.</t>
   </si>
   <si>
-    <t>The 2q13 copy number variation syndrome can result in the loss of up to 25 protein-coding genes. Patients with 2q13 deletions and duplications had abnormal head size and dysmorphic features (DOI: 10.1002/ajmg.a.37269). 2q13 duplications also caused developmental delay. The abnormal head size in 2q13 could be explained by the changes in FBLN7 gene (DOI: 10.1002/ajmg.a.37269). At the same time, neuropsychiatric impairment in 2q13 may be associated with BCL2L11, ANAPC1, SLC1A1 and MERTK alterations (DOI: 10.1002/ajmg.b.32236).</t>
-  </si>
-  <si>
-    <t>10q11.21q11.23 copy number variation (CNV) syndrome is a rare genetic disorder caused by a deletion or duplication of genetic material on chromosome 10. The exact genetic location chr10:49,390,199-51,058,796 (GRCh37) was taken from Kirov et al. 2014</t>
-  </si>
-  <si>
-    <t>10q22q23 copy number variation syndrome is a rare genetic syndrome caused by a deletion or duplication in the region 10q22q23 of chromosome 10. The exact position (chr10:82,045,472-88,931,651, GRCh37) was taken from Kirov et al. 2014. Patients usually suffer from developmental delay and psychiatric disorders as well as facial dyspmorphisms, and cardiac abnormalities.</t>
-  </si>
-  <si>
-    <t>A deletion in 11p11.2 can cause the Potocki-Shaffer syndrome (MIM # 601224) which is characterised by malformations in the heart, kidney and urinary tract.</t>
-  </si>
-  <si>
-    <t>Deletion or duplication of the CRYL1 gene located at chromosome 13q12 (chr13:20977806-21100012 (GRCh37)) is a risk factor for psychiatric disorders (Kirov et al. 2014).</t>
-  </si>
-  <si>
-    <t>Copy number variations in the region 13q12.12 (exact position: chr13:23555358-24884622 (GRCh37), numbers from Kirov et al. 2014 10.1016/j.biopsych.2013.07.022 ) are rare, pathological mutations in the human genome. It is a risk variation for neuropsychiatric diseases like schizophrenia (Kirov et al. 2014, 10.1016/j.biopsych.2013.07.022) and with the presence of SACS it harbors a gene known for causing Spastic ataxia (MIM # 270550).</t>
-  </si>
-  <si>
-    <t>The 15q11.2 deletion or duplication syndromes, also known as Burnside-Butler syndrome (BBS). This region is relatively small compared to other CNVs but it contains NIPA1 and NIPA2, two important magnesium transporters, which are active in the central nervous system. CYFIP1 is an important interactor with FMR1, which is the causative gene for fragile X syndrome. The breakpoints (chr15:22,805,313-23,094,530 GRCh37/hg19) are defined as given in Kendall et al. 2017: https://doi.org/10.1016/j.biopsych.2016.08.014.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prader-Willi syndrome (PWS) and Angelman syndrome (AS) are diseases that are both caused by a deletion in the same region of chromosome 15, namely 15q11-q13 (exact position chr15:22805313-28390339 (GRCh37) taken from Kirov et al. 2014). Due to methylation patterns however, different genes are responsible for the two syndromes. For this chromosomal region, also duplications are known.  A detailed description of the syndromes in this region and the molecular pathway has been published by Ehrhart et al. (https://doi.org/10.1080/15622975.2018.1439594). </t>
-  </si>
-  <si>
-    <t>The major genes in this region are OTUD7A and CHRNA7 which are known influencers of neuronal development and function. For several genes in this regio there are no exact functions known yet - e.g. the GOLGA gene group or the MTMR10 which is similar to phosphatidyl-inositol 3 phosphatases but without an active catalytic centre. The breakpoints 30,500,000-32,500,000 are from “15q13.3 Microdeletion”, Bregje WM van Bon et al. in Gene reviews PMID: 20301295.</t>
-  </si>
-  <si>
-    <t> 15q25 copy number variations are rare genetic disorders that cause neuropsychiatric disorders, developmental delay and cardiac abnormalities. The exact chromosomal position for this pathway (chr15:83219735-85722039, GRCh37) was taken from Kirov et al. 2014 10.1016/j.biopsych.2013.07.022.</t>
-  </si>
-  <si>
-    <t>16p11.2 distal deletion syndrome is a rare genetic disorder (copy number variation) caused by a deletion on chromosome 16 in the range 28.74-28.95-Mb. The breakpoints in this pathway are chr16:28,823,196-29,046,783 (GHCh37) from Kendall et al. 2017 https://doi.org/10.1016/j.biopsych.2016.08.014.</t>
-  </si>
-  <si>
-    <t>16p11.2 proximal deletion syndrome is a rare genetic disorder (copy number variation) caused by a deletion in the region of chromosome 16 from 29,592,751 to 30,190,593 bp (GRCh37). The breakpoints are from: Dell’Edera 2018 PMID: 29609622.</t>
-  </si>
-  <si>
-    <t>Copy number variations in the region 16p12.2 are rare, pathological mutations in the human genome. It is a risk variation for neuropsychiatric diseases like schizophrenia (Kirov et al. 2014, 10.1016/j.biopsych.2013.07.022)</t>
-  </si>
-  <si>
-    <t>Copy number variations in the region 16p13.11 are risks for neuropsychiatric diseases like schizophrenia (Kirov et al. 2014, 10.1016/j.biopsych.2013.07.022).</t>
-  </si>
-  <si>
-    <t>The 17p13.3 deletion or duplication ranging from chr17:1250000 to chr17:1300000, affects YWHAE gene. The YWHAE gene plays a role in a lot of different processes and is closely related to many diseases.</t>
-  </si>
-  <si>
-    <t>The NF1 deletion and NF1 duplication, ranging from chr17: 29,100,000 to chr17: 30,280,000 can result in a loss of up to 14 protein coding genes, including NF1.</t>
-  </si>
-  <si>
-    <t>The 2q21.1 copy number variation syndrome can result in the loss of up to 9 protein-coding genes. Deletions and duplications in 2q21.1 were reported to be connected to intellectual disability, hyperactivity, and aggressive behavior (DOI: 10.1002/mgg3.1135,DOI: 10.1002/ajmg.a.36357). The clinical picture was explained by alterations in five genes important for neurological development, namely GPR148, FAM123C, ARHGEF4, FAM168B and PLEKHB2 (DOI: 10.1002/ajmg.a.36357,DOI: 10.1093/hmg/dds166). Analogically, changes in tubulin genes in 2q21.1 were linked to Motor Timing in ADHD (DOI: 10.1016/j.ajhg.2008.06.006). For this rare disorder, two different genomic locations are known according to Kirov et al. 2014, and Gimelli et al. 2014 with a larger deletion.</t>
-  </si>
-  <si>
-    <t>The 2q37 copy number variation syndrome can result in the loss of up to 78 protein-coding genes. Patients with 2q37 CNV syndrome have intellectual disability, facial dysmorphism and skeletal and digit malformations (DOI: 10.1186/1755-8794-7-19, DOI: 10.1016/j.gene.2013.06.056). Research linked changes in HDAC4 gene with obesity of 2q37 patients (DOI: 10.1016/j.gene.2013.06.056). Chromosomal locations are from Kirov et al. 2014 (chr2:239,716,679-243,199,373) and the larger one from Sakai et al. 2014 (chr2:234,275,216-243,199,373).</t>
-  </si>
-  <si>
-    <t>The Wolf-Hirschhorn syndrome is a rare genetic disorder caused by a microdeletion in the chromosomal region 4p16.3. Typical symptoms are a distinct facial morphology, intellectual disability, psychiatric disorders, seizures, and heart defects. The chromosomal position chr4:1,552,030-2,091,303 (GCRh37) was taken from Kirov et al. 2014 (10.1016/j.biopsych.2013.07.022).</t>
-  </si>
-  <si>
     <t>A deletion in the chromosomal region 5q35 can cause the rare genetic disorder Sotos syndrome. Sotos syndrome is characterised by psychiatric disorders (autism, intellectual disability, developmental delay) and excessive growth. Also, duplication of 5q35 has been recorded.</t>
   </si>
   <si>
-    <t>7q11.23 copy number variation syndrome (MIM 609757, also called Williams-Beuren region duplication syndrome, WBS duplication syndrome, Chromosome 7q11.23 duplication syndrome, or Somerville-van-der-Aa syndrome) is a copy number variation syndrome with a duplication in the region chr7:72,744,454-74,142,513 (GRCh37/hg19). The breakpoint is defined from Carolyn B Mervis 7q11.23 Duplication Syndrome in Gene Reviews PMID: 20301295.</t>
-  </si>
-  <si>
-    <t>Deletion or duplication of the region chr7:75,138,294-76,064,412, also known as 7q11.23 distal (OMIM # 613729), are rare genetic disorders and can cause different neurological and neuropsychiatric symptoms. Patients are often observed with epilepsy and neurodevelopmental delay.</t>
-  </si>
-  <si>
-    <t>RB1CC1, located on chromosome 8q11.23, is mainly involved in autophagy regulation. A loss of function or mutation in the gene can result in increased risk for schizophrenia (Degenhardt et al. 2013).</t>
-  </si>
-  <si>
-    <t>Patients with a deletion often suffer from diaphragmatic hernia (CDH) and cardiac defects.</t>
-  </si>
-  <si>
-    <t>PAFAH1B1 located on chromosome 17p13.3 (exact position chr17:2496923-2588909, GRCh37, position from Kirov et al. 2014 10.1016/j.biopsych.2013.07.022) is responsible for the rare genetic disorder Miller-Dieker syndrome (MIM # 247200). The most common symptom is lisencephaly causing severe intellectual disability, cardiac and facial dysmorphic features. The protein is part of the type I platelet-activating factor acetylhydrolase and involved in stabilising dynein binding to microtubules.</t>
-  </si>
-  <si>
-    <t>The Smith-Magenis syndrome, is the result from a deletion of chr17:chr17:16,82-18,28, while the Potocki-Lupski syndrome is the result of a duplication of this area.</t>
+    <t>21948486;27602560;34207052;17531565</t>
+  </si>
+  <si>
+    <t>17436248;22970919;27031267;28588438;21248748</t>
+  </si>
+  <si>
+    <t>8882796;20140962;33126574;28127865;22770980</t>
+  </si>
+  <si>
+    <t>21359847;25689425;25596525;19328872;30767844</t>
+  </si>
+  <si>
+    <t>21290787;18805830;20236110;20301295</t>
+  </si>
+  <si>
+    <t>23239641;24352913;25217958</t>
+  </si>
+  <si>
+    <t>20808231;19966786;20799338;30767844</t>
+  </si>
+  <si>
+    <t>28542865;27929632;40390087;23813913;32323081</t>
+  </si>
+  <si>
+    <t>22q11.2 distal CNV</t>
+  </si>
+  <si>
+    <t>WP5546</t>
+  </si>
+  <si>
+    <t>22q11.2</t>
+  </si>
+  <si>
+    <t>Chr22:21920127-23653646</t>
+  </si>
+  <si>
+    <t>UBE2L3,YDJC,CCDC116,SDF2L1,PPIL2,YPEL1,MAPK1,PPM1F,TOP3B,VPREB1,ZNF280B,ZNF280A,PRAME,GGTLC2,IGLL5,RSPH14,GNAZ,RAB36,BCR</t>
+  </si>
+  <si>
+    <t>261330(microdeletion),261337(microduplication)</t>
+  </si>
+  <si>
+    <t>region_hg38</t>
+  </si>
+  <si>
+    <t>Chr10:48182156-49850750</t>
+  </si>
+  <si>
+    <t>Chr10:80285716-87171894</t>
+  </si>
+  <si>
+    <t>Chr11:43918450-45998449</t>
+  </si>
+  <si>
+    <t>Chr13:20403667-20525873</t>
+  </si>
+  <si>
+    <t>Chr13:22981219-24310484</t>
+  </si>
+  <si>
+    <t>Chr15:22778538-23067755</t>
+  </si>
+  <si>
+    <t>Chr15:28917241-32170575</t>
+  </si>
+  <si>
+    <t>Chr15:30207797-32207799</t>
+  </si>
+  <si>
+    <t>Chr15:82550985-85178808</t>
+  </si>
+  <si>
+    <t>Chr16:28811875-29035462</t>
+  </si>
+  <si>
+    <t>Chr16:29581430-30179272</t>
+  </si>
+  <si>
+    <t>Chr16:21938814-22420568</t>
+  </si>
+  <si>
+    <t>Chr16:15417798-16199832</t>
+  </si>
+  <si>
+    <t>Chr17:36460090-37857812</t>
+  </si>
+  <si>
+    <t>Chr17:1344540-1400262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chr1:65419-2563829 </t>
+  </si>
+  <si>
+    <t>Chr1:147056425-147922330</t>
+  </si>
+  <si>
+    <t>Chr2:96076661-97011779</t>
+  </si>
+  <si>
+    <t>Chr2:130723735-131173104</t>
+  </si>
+  <si>
+    <t>Chr3:196061428-197306425</t>
+  </si>
+  <si>
+    <t>Chr4:1550303-2089576</t>
+  </si>
+  <si>
+    <t>Chr5:176293921-177625593</t>
+  </si>
+  <si>
+    <t>Chr7:73330451-74728175</t>
+  </si>
+  <si>
+    <t>Chr8:8701937-12015049</t>
+  </si>
+  <si>
+    <t>Chr8:52622458-52745843</t>
+  </si>
+  <si>
+    <t>Chr2:110122311-110205066</t>
+  </si>
+  <si>
+    <t>Chr17:30772982-31952981</t>
+  </si>
+  <si>
+    <t>Chr17:2593183-2685615</t>
+  </si>
+  <si>
+    <t>Chr15:22983192-28322179</t>
+  </si>
+  <si>
+    <t>Chr17:16909457-18363550</t>
+  </si>
+  <si>
+    <t>Chr2:238808038-241873823</t>
+  </si>
+  <si>
+    <t>Chr1:145607988-146036746</t>
+  </si>
+  <si>
+    <t>Chr22:21565838-23311459</t>
+  </si>
+  <si>
+    <t>739(deletion),72(deletion),238446(microduplication),3306(inverted duplication)</t>
+  </si>
+  <si>
+    <t>31402777;36913617; 15138899;10839884</t>
+  </si>
+  <si>
+    <t>ACOXL,BCL2L11,ANAPC1,MERTK,TMEM87B,FBLN7,ZC3H8,ZC3H6,RGPD8,TTL,POLR1B,CHCHD5,SLC20A1,NT5DC4,CKAP2L,IL1A,IL1B,IL36,IL36G,IL36A,IL36B,IL36RN,IL1F10,IL1RN,PSD4</t>
+  </si>
+  <si>
+    <t>Chr2:110732539-113209396</t>
+  </si>
+  <si>
+    <t>684742(microdeletion)</t>
+  </si>
+  <si>
+    <t>26227573;24807792;24694933;34763108</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8116612; 8585580</t>
+  </si>
+  <si>
+    <t>40390087;12621583</t>
+  </si>
+  <si>
+    <t>36369750;26345236</t>
+  </si>
+  <si>
+    <t>32227665;21348049;37357910</t>
+  </si>
+  <si>
+    <t>21824431;37881147</t>
+  </si>
+  <si>
+    <t>23765049;26247050;41360439</t>
+  </si>
+  <si>
+    <t>36010058;34845825;27189754</t>
+  </si>
+  <si>
+    <t>26227573;25217958</t>
+  </si>
+  <si>
+    <t>38421086;27656750;33039685;37691301;33564151</t>
+  </si>
+  <si>
+    <t>30244530;36526544</t>
+  </si>
+  <si>
+    <t>33389145;36458506;8092192;15942875</t>
+  </si>
+  <si>
+    <t>21109226;20101691;27867344;35481155</t>
+  </si>
+  <si>
+    <t>37123967;20969981;19606479;26097203</t>
+  </si>
+  <si>
+    <t>20301505;20301323;39804213;8050626;21359847</t>
+  </si>
+  <si>
+    <t>23255863;29329513;34699703</t>
+  </si>
+  <si>
+    <t>region_hg17</t>
+  </si>
+  <si>
+    <t>distal-type- I,D-E,D-F</t>
+  </si>
+  <si>
+    <t>Chr7:75138294-76064412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chr2:111490116-113966973 </t>
+  </si>
+  <si>
+    <t>Chr22:18912777-21064168</t>
+  </si>
+  <si>
+    <t>Chr7:75842602-76435095</t>
+  </si>
+  <si>
+    <t>Chr22:51113070-51171640</t>
+  </si>
+  <si>
+    <t>Chr22:50674642-50733212</t>
+  </si>
+  <si>
+    <t>SHANK3</t>
+  </si>
+  <si>
+    <t>22q13.33</t>
+  </si>
+  <si>
+    <t>WP5566</t>
+  </si>
+  <si>
+    <t>SHANK3 pathway involved in Phelan-McDermid syndrome</t>
+  </si>
+  <si>
+    <t>48652(deletion)</t>
+  </si>
+  <si>
+    <t>22389789;17975801;11391650;30537371;20385823</t>
+  </si>
+  <si>
+    <t>WP5367</t>
+  </si>
+  <si>
+    <t>Rubinstein-Taybi syndrome 1</t>
+  </si>
+  <si>
+    <t>Chr16:3775056-3930121</t>
+  </si>
+  <si>
+    <t>Chr16:3725055-3880120</t>
+  </si>
+  <si>
+    <t>16p13.3</t>
+  </si>
+  <si>
+    <t>96078(microduplication),353281(microdeletion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A deletion, or a point mutation of the SHANK3 gene causes Phelan-McDermid syndrome, while the duplications are more rare. </t>
+  </si>
+  <si>
+    <t>19833603;20587603;21792059;9677064;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A microdeletion in this region, affecting CREBBP gene, causes Rubinstein-Taybi syndrome. Duplications of CREBBP in this region have also been reported. </t>
+  </si>
+  <si>
+    <t>CREBBP</t>
+  </si>
+  <si>
+    <t>The 2q13 copy number variation syndrome can result in the loss of up to 25 protein-coding genes. Patients with 2q13 deletions and duplications had abnormal head size and dysmorphic features. The abnormal head size in 2q13 could be explained by the changes in FBLN7 gene. At the same time, neuropsychiatric impairment in 2q13 may be associated with BCL2L11, ANAPC1, SLC1A1 and MERTK alterations.</t>
+  </si>
+  <si>
+    <t>21248749;25077648;19455185;19372089;29425059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10q11.21q11.23 copy number variation (CNV) syndrome is a rare genetic disorder caused by a deletion or duplication affecting 16 protein coding genes. </t>
+  </si>
+  <si>
+    <t>10q22q23 copy number variation syndrome is a rare genetic syndrome caused by a deletion or duplication affecting 25 protein coding genes. Patients usually suffer from developmental delay and psychiatric disorders as well as facial dyspmorphisms, and cardiac abnormalities.</t>
+  </si>
+  <si>
+    <t>A deletion in 11p11.2 can cause the Potocki-Shaffer syndrome which is characterised by malformations in the heart, kidney and urinary tract.</t>
+  </si>
+  <si>
+    <t>30767844;23992924</t>
+  </si>
+  <si>
+    <t>The 15q11.2 deletion or duplication in htis region involve 4 genes. The deletion is also known as Burnside-Butler syndrome (BBS) (MIM # 615656). This region contains NIPA1 and NIPA2, two important magnesium transporters, which are active in the central nervous system. CYFIP1 is an important interactor with FMR1, which is the causative gene for fragile X syndrome (MIM # 300624).</t>
+  </si>
+  <si>
+    <t>The major genes in this region are OTUD7A and CHRNA7 which are known influencers of neuronal development and function. For several genes in this region there are no exact functions known yet - e.g. the GOLGA gene group or the MTMR10 which is similar to phosphatidyl-inositol 3 phosphatases but without an active catalytic centre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q25 copy number variations are rare genetic disorders that cause neuropsychiatric disorders, developmental delay and cardiac abnormalities. </t>
+  </si>
+  <si>
+    <t>16p11.2 proximal copy number variation includes 26 protein coding genes. Deletion and duplications in this region confer susceptibility to autism spectrum disorder (ASD) in up to 1% of ASD patients, (Fernandez et al., 2010). The deletions in this region are also associated with severe early-onset obesity  (Bochukova et al., 2010).</t>
+  </si>
+  <si>
+    <t>20301775;33667823;19755429;29609622;19966786</t>
+  </si>
+  <si>
+    <t>16p11.2 distal copy number variation includes 9 protein coding genes. An important gene hoever is SH2B1 (MIM # 608937) which is associated with obesity and developmental delay Bachmann-(Gagescu et al., 2010).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This region is mainly know for its deletion that causes Prader-Willi syndrome (PWS) and Angelman syndrome (AS). Due to methylation patterns however, different genes are responsible for the two syndromes. For this chromosomal region, also duplications are known.  A detailed description of the syndromes in this region and the molecular pathway has been published by Ehrhart et al., 2017 . </t>
+  </si>
+  <si>
+    <t>Copy number variations in the region 13q12.12 are rare, pathological mutations in the human genome. It is a risk variation for neuropsychiatric diseases like schizophrenia (Kirov et al., 2014), and with the presence of SACS it harbors a gene known for causing Spastic ataxia (MIM # 270550).</t>
+  </si>
+  <si>
+    <t>Deletion or duplication of the CRYL1 gene located at chromosome 13q12 is a risk factor for psychiatric disorders as reported by (Kirov et al., 2014).</t>
+  </si>
+  <si>
+    <t>Copy number variations in the region 16p12.2 are rare, pathological mutations in the human genome. It is a risk variation for neuropsychiatric diseases like schizophrenia (Kirov et al., 2014)</t>
+  </si>
+  <si>
+    <t>30767844;24352232;30190612;23992924</t>
+  </si>
+  <si>
+    <t>Copy number variations in the region 16p13.11 are risks for neuropsychiatric diseases like schizophrenia (Kirov et al., 2014).</t>
+  </si>
+  <si>
+    <t>30287593;36724812;40256007;20398883;23992924</t>
+  </si>
+  <si>
+    <t>This region includes 24 protein coding genes. The deletion causes Smith-Magenis syndrome, while the the duplication causes Potocki-Lupski syndrome.</t>
+  </si>
+  <si>
+    <t>The 17p13.3 deletion or duplication affects YWHAE (MIM # 605066) gene. YWHAE plays a role in a lot of different processes and is closely related to many diseases.</t>
+  </si>
+  <si>
+    <t>The deletion or point mutation of PAFAH1B1 (LIS1, MIM # 601545) is responsible for the rare genetic disorder Miller-Dieker syndrome (MIM # 247200). The most common symptom is lisencephaly causing severe intellectual disability, cardiac and facial dysmorphic features. The protein is part of the type I platelet-activating factor acetylhydrolase and involved in stabilising dynein binding to microtubules.</t>
+  </si>
+  <si>
+    <t>The NF1 deletion and duplication can result in a loss of up to 14 protein coding genes, including NF1 (MIM # 613113).</t>
+  </si>
+  <si>
+    <t>The 2q21.1 copy number variation syndrome can result in the loss of up to 9 protein-coding genes. Deletions and duplications in 2q21.1 were reported to be connected to intellectual disability, hyperactivity, and aggressive behavior (Almuzzaini et al., 2020; Gimelli et al., 2014). The clinical picture was explained by alterations in five genes important for neurological development, namely GPR148, FAM123C, ARHGEF4, FAM168B and PLEKHB2 (Gimelli et al., 2014; Dharmadhikari et al., 2012). Analogically, changes in tubulin genes in 2q21.1 were linked to Motor Timing in ADHD (Rommelse et al., 2008). For this rare disorder, two different genomic locations are known according to Kirov et al. 2014, and Gimelli et al. 2014 with a larger deletion.</t>
+  </si>
+  <si>
+    <t>22543972;24591035;25661985;31989799;18599010;23992924</t>
+  </si>
+  <si>
+    <t>20691407;19752160;7847374;36833393;24755370;23895799</t>
+  </si>
+  <si>
+    <t>The 2q37 copy number variation syndrome can result in the loss of up to 78 protein-coding genes. Patients with 2q37 CNV syndrome have intellectual disability, facial dysmorphism and skeletal and digit malformations (Sakai et al., 2014; López-Uriarte et al., 2013). Research linked changes in HDAC4 gene with obesity of 2q37 patients (López-Uriarte et al., 2013). Chromosomal locations are from Kirov et al. 2014, and the larger one from Sakai et al. 2014.</t>
+  </si>
+  <si>
+    <t>Microdeletion in this region causes Wolf-Hirschhorn syndrome. Typical symptoms are a distinct facial morphology, intellectual disability, psychiatric disorders, seizures, and heart defects.</t>
+  </si>
+  <si>
+    <t>33610060;20089974;19249392;26610320</t>
+  </si>
+  <si>
+    <t>7q11.23 copy number variation syndrome (MIM 609757, also called Williams-Beuren region duplication syndrome, WBS duplication syndrome, Chromosome 7q11.23 duplication syndrome, or Somerville-van-der-Aa syndrome) is a duplication syndrome. The breakpoints are defined from Mervis et al., 2015.</t>
+  </si>
+  <si>
+    <t>Deletion or duplication in this region are rare genetic disorders and can cause different neurological and neuropsychiatric symptoms. Patients are often observed with epilepsy and neurodevelopmental delay.</t>
+  </si>
+  <si>
+    <t>Deletion and duplications in this region involve 23 protein coding genes. Patients with a deletion often suffer from diaphragmatic hernia (CDH) and cardiac defects.</t>
+  </si>
+  <si>
+    <t>RB1CC1, located on chromosome 8q11.23, is mainly involved in autophagy regulation (MIM # 606837). A loss of function or mutation in the gene can result in increased risk for schizophrenia (Degenhardt et al., 2013; Errichiello et al., 2020).</t>
+  </si>
+  <si>
+    <t>26151896;33340270</t>
+  </si>
+  <si>
+    <t>27929632;27409573;41465172;26925472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This region contains HNF1B (TCF2, MIM # 189907) gene with early expressions in the kidney, liver, bile ducts, thymus, genital tract, pancreas, lung, and gut. The deletion in this region causes Renal Cysts and Diabetes (RCAD) syndrome (MIM # 137920). </t>
+  </si>
+  <si>
+    <t>The deletion in this region is known as TAR syndrome (Thrombocytopenia with Absent Radius). A landmark gene for this region is RBM8A (MIM # 605313).</t>
+  </si>
+  <si>
+    <t>1p36.33-p36.32 deletion or duplication syndromes are rare genetic disorders caused by a deletion or duplication of the most distal light band of the short arm of chromosome 1. It affects around 60 protein coding genes.</t>
   </si>
 </sst>
 </file>
@@ -1945,7 +2239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1961,30 +2255,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2019,37 +2289,44 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2356,1057 +2633,1349 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.88671875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="10" customWidth="1"/>
-    <col min="3" max="3" width="14" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.88671875" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="41.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.88671875" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="61.109375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="15" customWidth="1"/>
+    <col min="3" max="3" width="14" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="15" customWidth="1"/>
+    <col min="6" max="6" width="51.21875" style="13" customWidth="1"/>
+    <col min="7" max="7" width="37.5546875" style="15" customWidth="1"/>
+    <col min="8" max="8" width="24.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.5546875" style="15" customWidth="1"/>
+    <col min="10" max="10" width="40.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="40.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>221</v>
+      <c r="F1" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>223</v>
-      </c>
       <c r="K1" s="7" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="138" customHeight="1" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="138" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="F2" s="29"/>
-      <c r="G2" s="8" t="s">
+      <c r="D3" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J2" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="I3" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="K3" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E3" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="F3" s="29"/>
-      <c r="G3" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="D4" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="J3" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="29" t="s">
-        <v>260</v>
-      </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="I4" s="9" t="s">
+      <c r="D5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="I5" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="K5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" t="s">
-        <v>261</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="D6" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="I6" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" t="s">
-        <v>262</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>81</v>
-      </c>
       <c r="K6" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="F7" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E7" t="s">
+      <c r="C8" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="E8" s="25"/>
+      <c r="F8" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="K8" s="14"/>
+      <c r="L8" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="K9" s="14"/>
+      <c r="L9" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>255</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="18"/>
+      <c r="F14" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="25"/>
+      <c r="F16" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="K16" s="14"/>
+      <c r="L16" s="9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="160.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="96" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E19" s="25"/>
+      <c r="F19" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="28"/>
+      <c r="F20" s="29" t="s">
+        <v>378</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>377</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="I20" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="K20" s="29"/>
+      <c r="L20" s="22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="25"/>
+      <c r="F21" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="26"/>
+      <c r="F23" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="K23" s="27"/>
+      <c r="L23" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>259</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="H7" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="K7" s="31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="29"/>
-      <c r="E8" t="s">
-        <v>264</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="J8" s="35"/>
-      <c r="K8" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" t="s">
-        <v>265</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="J9" s="35"/>
-      <c r="K9" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" t="s">
-        <v>266</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J10" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="K10" s="32" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D11" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" s="29" t="s">
-        <v>267</v>
-      </c>
-      <c r="F11" s="29"/>
-      <c r="G11" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" t="s">
-        <v>268</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="F13" s="28"/>
-      <c r="G13" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="H13" s="9" t="s">
+      <c r="E24" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="H24" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="I24" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="K25" s="14"/>
+      <c r="L25" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="14"/>
+      <c r="L26" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="146.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="G29" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I29" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="G30" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="I30" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="I31" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31" s="14"/>
+      <c r="L31" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E34" s="25"/>
+      <c r="F34" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L34" s="17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E35" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="J13" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>270</v>
-      </c>
-      <c r="F14" s="28"/>
-      <c r="G14" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="J14" s="35"/>
-      <c r="K14" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="F15" s="29"/>
-      <c r="G15" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="H16" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="I16" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="160.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="F35" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="28"/>
-      <c r="G17" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="H17" s="9" t="s">
+      <c r="B36" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="J36" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="I17" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="8" t="s">
+      <c r="L36" s="14" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A37" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="D37" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="F18" s="28"/>
-      <c r="G18" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D19" s="29"/>
-      <c r="E19" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="F19" s="28"/>
-      <c r="G19" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E20" t="s">
-        <v>255</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="D21" s="29"/>
-      <c r="E21" t="s">
-        <v>257</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J21" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" t="s">
-        <v>273</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J22" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30" t="s">
-        <v>274</v>
-      </c>
-      <c r="F23" s="30"/>
-      <c r="G23" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="H23" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="I23" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="J23" s="36"/>
-      <c r="K23" s="32" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="F24" s="28"/>
-      <c r="G24" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="J24" s="35"/>
-      <c r="K24" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="E25" t="s">
-        <v>275</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="E26" t="s">
-        <v>276</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="J26" s="35"/>
-      <c r="K26" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="146.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="E27" t="s">
-        <v>277</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="F37" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="H37" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="E28" t="s">
-        <v>278</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="E29" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="F29" s="29"/>
-      <c r="G29" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="H29" s="25" t="s">
-        <v>250</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="I37" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="J37" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="F30" s="29"/>
-      <c r="G30" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J30" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="E31" t="s">
-        <v>272</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J31" s="35"/>
-      <c r="K31" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" t="s">
-        <v>256</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J32" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33" t="s">
-        <v>281</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D34" s="29"/>
-      <c r="E34" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="F34" s="28"/>
-      <c r="G34" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="K34" s="34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="E35" t="s">
-        <v>282</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="J35" s="35"/>
-      <c r="K35" s="9" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E36" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="F36" s="28"/>
-      <c r="G36" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>38</v>
+      <c r="K37" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L37" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K36" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K36">
-      <sortCondition ref="A1:A36"/>
+  <autoFilter ref="A1:L37" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L37">
+      <sortCondition ref="C1:C36"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3426,18 +3995,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3474,557 +4043,554 @@
   <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.88671875" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" style="23" customWidth="1"/>
-    <col min="3" max="4" width="40.88671875" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" style="23" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="23"/>
+    <col min="1" max="1" width="34.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" style="15" customWidth="1"/>
+    <col min="3" max="4" width="40.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" style="15" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="14" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="E1" s="24" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="D2" s="17" t="s">
+      <c r="B36" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="13" t="s">
         <v>244</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/cnv_data.xlsx
+++ b/data/input/cnv_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\alexandra\chapter1\cnv-data\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5178E8B6-81BB-4434-907E-322BC1829FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA33EA7F-D3F6-4AB1-9EDC-64F95BBF063D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="382">
   <si>
     <t xml:space="preserve">in my retrieved gene, but not in the wikipathways </t>
   </si>
@@ -1632,12 +1632,6 @@
     <t>3320(deletion)</t>
   </si>
   <si>
-    <t>1q21.1 copy number variation (deletion or duplication)  can result in the loss or duplication of up to 7 protein-coding genes, leading to widespread effects on human development. The syndromes are known for a highly variable phenotype especially concerning psychiatric problems. The breakpoints (chr1:146,527,987-147,394,444, GRCh37/hg19) are defined as given in Kendall et al. 2017: https://doi.org/10.1016/j.biopsych.2016.08.014.</t>
-  </si>
-  <si>
-    <t>The 2q11.2 copy number variation syndrome can result in the loss of up to 27 protein-coding genes. Patients with 2q11.2 deletions were reported to have developmental delay, speech delay and ADHD, while subjects with 2q11.2 duplications apart from developmental delay had gastroesophageal reflux and short stature (DOI: 10.1002/ajmg.a.37269).</t>
-  </si>
-  <si>
     <t>Mutations or loss of NPHP1 cause nephronophthisis (NPHP), a rare genetic disorder. Due to the involvement of NPHP1 in ciliary function and cellular orientation in kidney, the main symptoms of the disorder are found in kidney development and function. However, as in many ciliopathies, neuronal functions are also affected, causing psychiatric disorders.</t>
   </si>
   <si>
@@ -1854,9 +1848,6 @@
     <t>region_hg17</t>
   </si>
   <si>
-    <t>distal-type- I,D-E,D-F</t>
-  </si>
-  <si>
     <t>Chr7:75138294-76064412</t>
   </si>
   <si>
@@ -1941,9 +1932,6 @@
     <t>30767844;23992924</t>
   </si>
   <si>
-    <t>The 15q11.2 deletion or duplication in htis region involve 4 genes. The deletion is also known as Burnside-Butler syndrome (BBS) (MIM # 615656). This region contains NIPA1 and NIPA2, two important magnesium transporters, which are active in the central nervous system. CYFIP1 is an important interactor with FMR1, which is the causative gene for fragile X syndrome (MIM # 300624).</t>
-  </si>
-  <si>
     <t>The major genes in this region are OTUD7A and CHRNA7 which are known influencers of neuronal development and function. For several genes in this region there are no exact functions known yet - e.g. the GOLGA gene group or the MTMR10 which is similar to phosphatidyl-inositol 3 phosphatases but without an active catalytic centre.</t>
   </si>
   <si>
@@ -1956,15 +1944,9 @@
     <t>20301775;33667823;19755429;29609622;19966786</t>
   </si>
   <si>
-    <t>16p11.2 distal copy number variation includes 9 protein coding genes. An important gene hoever is SH2B1 (MIM # 608937) which is associated with obesity and developmental delay Bachmann-(Gagescu et al., 2010).</t>
-  </si>
-  <si>
     <t xml:space="preserve">This region is mainly know for its deletion that causes Prader-Willi syndrome (PWS) and Angelman syndrome (AS). Due to methylation patterns however, different genes are responsible for the two syndromes. For this chromosomal region, also duplications are known.  A detailed description of the syndromes in this region and the molecular pathway has been published by Ehrhart et al., 2017 . </t>
   </si>
   <si>
-    <t>Copy number variations in the region 13q12.12 are rare, pathological mutations in the human genome. It is a risk variation for neuropsychiatric diseases like schizophrenia (Kirov et al., 2014), and with the presence of SACS it harbors a gene known for causing Spastic ataxia (MIM # 270550).</t>
-  </si>
-  <si>
     <t>Deletion or duplication of the CRYL1 gene located at chromosome 13q12 is a risk factor for psychiatric disorders as reported by (Kirov et al., 2014).</t>
   </si>
   <si>
@@ -1986,12 +1968,6 @@
     <t>The 17p13.3 deletion or duplication affects YWHAE (MIM # 605066) gene. YWHAE plays a role in a lot of different processes and is closely related to many diseases.</t>
   </si>
   <si>
-    <t>The deletion or point mutation of PAFAH1B1 (LIS1, MIM # 601545) is responsible for the rare genetic disorder Miller-Dieker syndrome (MIM # 247200). The most common symptom is lisencephaly causing severe intellectual disability, cardiac and facial dysmorphic features. The protein is part of the type I platelet-activating factor acetylhydrolase and involved in stabilising dynein binding to microtubules.</t>
-  </si>
-  <si>
-    <t>The NF1 deletion and duplication can result in a loss of up to 14 protein coding genes, including NF1 (MIM # 613113).</t>
-  </si>
-  <si>
     <t>The 2q21.1 copy number variation syndrome can result in the loss of up to 9 protein-coding genes. Deletions and duplications in 2q21.1 were reported to be connected to intellectual disability, hyperactivity, and aggressive behavior (Almuzzaini et al., 2020; Gimelli et al., 2014). The clinical picture was explained by alterations in five genes important for neurological development, namely GPR148, FAM123C, ARHGEF4, FAM168B and PLEKHB2 (Gimelli et al., 2014; Dharmadhikari et al., 2012). Analogically, changes in tubulin genes in 2q21.1 were linked to Motor Timing in ADHD (Rommelse et al., 2008). For this rare disorder, two different genomic locations are known according to Kirov et al. 2014, and Gimelli et al. 2014 with a larger deletion.</t>
   </si>
   <si>
@@ -2001,40 +1977,67 @@
     <t>20691407;19752160;7847374;36833393;24755370;23895799</t>
   </si>
   <si>
-    <t>The 2q37 copy number variation syndrome can result in the loss of up to 78 protein-coding genes. Patients with 2q37 CNV syndrome have intellectual disability, facial dysmorphism and skeletal and digit malformations (Sakai et al., 2014; López-Uriarte et al., 2013). Research linked changes in HDAC4 gene with obesity of 2q37 patients (López-Uriarte et al., 2013). Chromosomal locations are from Kirov et al. 2014, and the larger one from Sakai et al. 2014.</t>
-  </si>
-  <si>
     <t>Microdeletion in this region causes Wolf-Hirschhorn syndrome. Typical symptoms are a distinct facial morphology, intellectual disability, psychiatric disorders, seizures, and heart defects.</t>
   </si>
   <si>
     <t>33610060;20089974;19249392;26610320</t>
   </si>
   <si>
-    <t>7q11.23 copy number variation syndrome (MIM 609757, also called Williams-Beuren region duplication syndrome, WBS duplication syndrome, Chromosome 7q11.23 duplication syndrome, or Somerville-van-der-Aa syndrome) is a duplication syndrome. The breakpoints are defined from Mervis et al., 2015.</t>
-  </si>
-  <si>
     <t>Deletion or duplication in this region are rare genetic disorders and can cause different neurological and neuropsychiatric symptoms. Patients are often observed with epilepsy and neurodevelopmental delay.</t>
   </si>
   <si>
     <t>Deletion and duplications in this region involve 23 protein coding genes. Patients with a deletion often suffer from diaphragmatic hernia (CDH) and cardiac defects.</t>
   </si>
   <si>
-    <t>RB1CC1, located on chromosome 8q11.23, is mainly involved in autophagy regulation (MIM # 606837). A loss of function or mutation in the gene can result in increased risk for schizophrenia (Degenhardt et al., 2013; Errichiello et al., 2020).</t>
-  </si>
-  <si>
     <t>26151896;33340270</t>
   </si>
   <si>
     <t>27929632;27409573;41465172;26925472</t>
   </si>
   <si>
-    <t xml:space="preserve">This region contains HNF1B (TCF2, MIM # 189907) gene with early expressions in the kidney, liver, bile ducts, thymus, genital tract, pancreas, lung, and gut. The deletion in this region causes Renal Cysts and Diabetes (RCAD) syndrome (MIM # 137920). </t>
-  </si>
-  <si>
-    <t>The deletion in this region is known as TAR syndrome (Thrombocytopenia with Absent Radius). A landmark gene for this region is RBM8A (MIM # 605313).</t>
-  </si>
-  <si>
     <t>1p36.33-p36.32 deletion or duplication syndromes are rare genetic disorders caused by a deletion or duplication of the most distal light band of the short arm of chromosome 1. It affects around 60 protein coding genes.</t>
+  </si>
+  <si>
+    <t>distal-type-I,D-E,D-F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22q11.2 distal copy number variations (CNVs) are rare deletions or duplications located distal (telomeric) to the classic DiGeorge syndrome region, specifically between low copy repeats (LCR) D-E or D-F. They cause a distinct, highly variable syndrome with symptoms including developmental delay, speech difficulties, hypotonia, and mild dysmorphic features. </t>
+  </si>
+  <si>
+    <t>1q21.1 copy number variation (deletion or duplication)  can result in the loss or duplication of up to 7 protein-coding genes, leading to widespread effects on human development. The syndromes are known for a highly variable phenotype especially concerning psychiatric problems.</t>
+  </si>
+  <si>
+    <t>Copy number variations in the region 13q12.12 are rare, pathological mutations in the human genome. It is a risk variation for neuropsychiatric diseases like schizophrenia (Kirov et al., 2014), and with the presence of SACS it harbors a gene known for causing Spastic ataxia (MIM#270550).</t>
+  </si>
+  <si>
+    <t>The 15q11.2 deletion or duplication in htis region involve 4 genes. The deletion is also known as Burnside-Butler syndrome (BBS) (MIM#615656). This region contains NIPA1 and NIPA2, two important magnesium transporters, which are active in the central nervous system. CYFIP1 is an important interactor with FMR1, which is the causative gene for fragile X syndrome (MIM#300624).</t>
+  </si>
+  <si>
+    <t>16p11.2 distal copy number variation includes 9 protein coding genes. An important gene hoever is SH2B1 (MIM#608937) which is associated with obesity and developmental delay (Bachmann-Gagescu et al., 2010).</t>
+  </si>
+  <si>
+    <t>The deletion or point mutation of PAFAH1B1 (LIS1, MIM#601545) is responsible for the rare genetic disorder Miller-Dieker syndrome (MIM#247200). The most common symptom is lisencephaly causing severe intellectual disability, cardiac and facial dysmorphic features. The protein is part of the type I platelet-activating factor acetylhydrolase and involved in stabilising dynein binding to microtubules.</t>
+  </si>
+  <si>
+    <t>The NF1 deletion and duplication can result in a loss of up to 14 protein coding genes, including NF1 (MIM#613113).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This region contains HNF1B (TCF2, MIM#189907) gene with early expressions in the kidney, liver, bile ducts, thymus, genital tract, pancreas, lung, and gut. The deletion in this region causes Renal Cysts and Diabetes (RCAD) syndrome (MIM#137920). </t>
+  </si>
+  <si>
+    <t>The deletion in this region is known as TAR syndrome (Thrombocytopenia with Absent Radius). A landmark gene for this region is RBM8A (MIM#605313).</t>
+  </si>
+  <si>
+    <t>The 2q11.2 copy number variation syndrome can result in the loss of up to 27 protein-coding genes. Patients with 2q11.2 deletions were reported to have developmental delay, speech delay and ADHD, while subjects with 2q11.2 duplications apart from developmental delay had gastroesophageal reflux and short stature.</t>
+  </si>
+  <si>
+    <t>The 2q37 copy number variation syndrome can result in the loss of up to 78 protein-coding genes. Patients with 2q37 CNV syndrome have intellectual disability, facial dysmorphism and skeletal and digit malformations (Sakai et al., 2014; López-Uriarte et al., 2013). Research linked changes in HDAC4 gene with obesity of 2q37 patients (López-Uriarte et al., 2013). Chromosomal locations are from Kirov et al. 2014, and the larger one from Sakai et al., 2014.</t>
+  </si>
+  <si>
+    <t>7q11.23 copy number variation syndrome (MIM#609757, also called Williams-Beuren region duplication syndrome, WBS duplication syndrome, Chromosome 7q11.23 duplication syndrome, or Somerville-van-der-Aa syndrome) is a duplication syndrome. The breakpoints are defined from Mervis et al., 2015.</t>
+  </si>
+  <si>
+    <t>RB1CC1, located on chromosome 8q11.23, is mainly involved in autophagy regulation (MIM#606837). A loss of function or mutation in the gene can result in increased risk for schizophrenia (Degenhardt et al., 2013; Errichiello et al., 2020).</t>
   </si>
 </sst>
 </file>
@@ -2674,10 +2677,10 @@
         <v>215</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>4</v>
@@ -2689,7 +2692,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="138" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>34</v>
       </c>
@@ -2703,16 +2706,16 @@
         <v>78</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>81</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>201</v>
@@ -2738,16 +2741,16 @@
         <v>85</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>84</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>50</v>
@@ -2773,16 +2776,16 @@
         <v>89</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G4" s="25" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>88</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>202</v>
@@ -2808,16 +2811,16 @@
         <v>52</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>92</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>52</v>
@@ -2843,16 +2846,16 @@
         <v>78</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>95</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>54</v>
@@ -2878,16 +2881,16 @@
         <v>99</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>98</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J7" s="19" t="s">
         <v>16</v>
@@ -2907,20 +2910,20 @@
         <v>101</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="17" t="s">
         <v>102</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>103</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>203</v>
@@ -2944,16 +2947,16 @@
         <v>107</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>106</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>204</v>
@@ -2977,16 +2980,16 @@
         <v>111</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>110</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="J10" s="20" t="s">
         <v>18</v>
@@ -3009,16 +3012,16 @@
         <v>78</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>114</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>58</v>
@@ -3047,16 +3050,16 @@
         <v>126</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>127</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>22</v>
@@ -3082,16 +3085,16 @@
         <v>130</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>131</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>20</v>
@@ -3115,16 +3118,16 @@
       </c>
       <c r="E14" s="18"/>
       <c r="F14" s="17" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>121</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>122</v>
@@ -3150,16 +3153,16 @@
         <v>118</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>117</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>64</v>
@@ -3183,16 +3186,16 @@
       </c>
       <c r="E16" s="25"/>
       <c r="F16" s="14" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>139</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>226</v>
@@ -3219,16 +3222,16 @@
         <v>43</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>135</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>43</v>
@@ -3254,16 +3257,16 @@
         <v>60</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>142</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>60</v>
@@ -3287,16 +3290,16 @@
       </c>
       <c r="E19" s="25"/>
       <c r="F19" s="13" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>146</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>41</v>
@@ -3320,16 +3323,16 @@
       </c>
       <c r="E20" s="28"/>
       <c r="F20" s="29" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="H20" s="21" t="s">
         <v>151</v>
       </c>
       <c r="I20" s="28" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J20" s="22" t="s">
         <v>152</v>
@@ -3354,16 +3357,16 @@
       </c>
       <c r="E21" s="25"/>
       <c r="F21" s="17" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>69</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>236</v>
@@ -3386,16 +3389,16 @@
         <v>245</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>73</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>37</v>
@@ -3419,16 +3422,16 @@
       </c>
       <c r="E23" s="26"/>
       <c r="F23" s="20" t="s">
-        <v>246</v>
+        <v>370</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H23" s="23" t="s">
         <v>77</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="J23" s="20" t="s">
         <v>10</v>
@@ -3440,36 +3443,38 @@
     </row>
     <row r="24" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>258</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="D24" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="H24" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="I24" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="J24" s="14" t="s">
         <v>260</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>320</v>
-      </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="H24" s="25" t="s">
-        <v>261</v>
-      </c>
-      <c r="I24" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="J24" s="14" t="s">
-        <v>262</v>
       </c>
       <c r="K24" s="14"/>
       <c r="L24" s="14" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -3489,13 +3494,13 @@
         <v>170</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>171</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>209</v>
@@ -3519,16 +3524,16 @@
         <v>78</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>247</v>
+        <v>378</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>167</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>24</v>
@@ -3549,28 +3554,28 @@
         <v>155</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="K27" s="17" t="s">
         <v>78</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -3590,16 +3595,16 @@
         <v>48</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>156</v>
       </c>
       <c r="I28" s="15" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>48</v>
@@ -3625,16 +3630,16 @@
         <v>78</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="G29" s="25" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>160</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>205</v>
@@ -3660,16 +3665,16 @@
         <v>164</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>163</v>
       </c>
       <c r="I30" s="25" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J30" s="9" t="s">
         <v>238</v>
@@ -3695,13 +3700,13 @@
         <v>175</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>176</v>
       </c>
       <c r="I31" s="18" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>12</v>
@@ -3725,16 +3730,16 @@
         <v>181</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>180</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>39</v>
@@ -3760,16 +3765,16 @@
         <v>185</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>184</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>45</v>
@@ -3793,16 +3798,16 @@
       </c>
       <c r="E34" s="25"/>
       <c r="F34" s="13" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>188</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>14</v>
@@ -3828,16 +3833,16 @@
         <v>126</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H35" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="I35" s="15" t="s">
         <v>321</v>
-      </c>
-      <c r="I35" s="15" t="s">
-        <v>324</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>230</v>
@@ -3861,16 +3866,16 @@
         <v>199</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>198</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J36" s="24" t="s">
         <v>243</v>
@@ -3893,16 +3898,16 @@
         <v>78</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="H37" s="18" t="s">
         <v>195</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="J37" s="17" t="s">
         <v>62</v>
@@ -3916,60 +3921,60 @@
     </row>
     <row r="38" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="15" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B38" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="G38" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="C38" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="G38" s="15" t="s">
-        <v>332</v>
-      </c>
       <c r="H38" s="15" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="D39" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="I39" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="C39" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>340</v>
-      </c>
-      <c r="H39" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="I39" s="15" t="s">
-        <v>336</v>
-      </c>
       <c r="J39" s="13" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -4418,10 +4423,10 @@
         <v>157</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">

--- a/data/input/cnv_data.xlsx
+++ b/data/input/cnv_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\alexandra\chapter1\cnv-data\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA33EA7F-D3F6-4AB1-9EDC-64F95BBF063D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E855A543-AD2F-4A25-83CE-F771D7148E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="20892" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cnv_input_table" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="383">
   <si>
     <t xml:space="preserve">in my retrieved gene, but not in the wikipathways </t>
   </si>
@@ -1809,9 +1809,6 @@
     <t>36369750;26345236</t>
   </si>
   <si>
-    <t>32227665;21348049;37357910</t>
-  </si>
-  <si>
     <t>21824431;37881147</t>
   </si>
   <si>
@@ -1998,9 +1995,6 @@
     <t>1p36.33-p36.32 deletion or duplication syndromes are rare genetic disorders caused by a deletion or duplication of the most distal light band of the short arm of chromosome 1. It affects around 60 protein coding genes.</t>
   </si>
   <si>
-    <t>distal-type-I,D-E,D-F</t>
-  </si>
-  <si>
     <t xml:space="preserve">22q11.2 distal copy number variations (CNVs) are rare deletions or duplications located distal (telomeric) to the classic DiGeorge syndrome region, specifically between low copy repeats (LCR) D-E or D-F. They cause a distinct, highly variable syndrome with symptoms including developmental delay, speech difficulties, hypotonia, and mild dysmorphic features. </t>
   </si>
   <si>
@@ -2038,6 +2032,15 @@
   </si>
   <si>
     <t>RB1CC1, located on chromosome 8q11.23, is mainly involved in autophagy regulation (MIM#606837). A loss of function or mutation in the gene can result in increased risk for schizophrenia (Degenhardt et al., 2013; Errichiello et al., 2020).</t>
+  </si>
+  <si>
+    <t>32227665;21348049;37357910;22317977</t>
+  </si>
+  <si>
+    <t>proximal,BP2-BP3</t>
+  </si>
+  <si>
+    <t>distal,type-I,D-E,D-F</t>
   </si>
 </sst>
 </file>
@@ -2677,7 +2680,7 @@
         <v>215</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>262</v>
@@ -2706,7 +2709,7 @@
         <v>78</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>248</v>
@@ -2741,7 +2744,7 @@
         <v>85</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>249</v>
@@ -2776,7 +2779,7 @@
         <v>89</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G4" s="25" t="s">
         <v>250</v>
@@ -2811,10 +2814,10 @@
         <v>52</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>92</v>
@@ -2846,10 +2849,10 @@
         <v>78</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>95</v>
@@ -2881,7 +2884,7 @@
         <v>99</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>251</v>
@@ -2917,7 +2920,7 @@
         <v>102</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>103</v>
@@ -2947,10 +2950,10 @@
         <v>107</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>106</v>
@@ -2980,7 +2983,7 @@
         <v>111</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G10" s="15" t="s">
         <v>252</v>
@@ -3012,7 +3015,7 @@
         <v>78</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>253</v>
@@ -3050,7 +3053,7 @@
         <v>126</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G12" s="15" t="s">
         <v>254</v>
@@ -3085,10 +3088,10 @@
         <v>130</v>
       </c>
       <c r="F13" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="G13" s="15" t="s">
         <v>348</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>349</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>131</v>
@@ -3118,10 +3121,10 @@
       </c>
       <c r="E14" s="18"/>
       <c r="F14" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="G14" s="18" t="s">
         <v>352</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>353</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>121</v>
@@ -3153,10 +3156,10 @@
         <v>118</v>
       </c>
       <c r="F15" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G15" s="8" t="s">
         <v>354</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>355</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>117</v>
@@ -3186,10 +3189,10 @@
       </c>
       <c r="E16" s="25"/>
       <c r="F16" s="14" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>139</v>
@@ -3222,7 +3225,7 @@
         <v>43</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G17" s="15" t="s">
         <v>255</v>
@@ -3257,7 +3260,7 @@
         <v>60</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G18" s="15" t="s">
         <v>303</v>
@@ -3290,7 +3293,7 @@
       </c>
       <c r="E19" s="25"/>
       <c r="F19" s="13" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G19" s="15" t="s">
         <v>302</v>
@@ -3323,10 +3326,10 @@
       </c>
       <c r="E20" s="28"/>
       <c r="F20" s="29" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H20" s="21" t="s">
         <v>151</v>
@@ -3357,7 +3360,7 @@
       </c>
       <c r="E21" s="25"/>
       <c r="F21" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G21" s="18" t="s">
         <v>304</v>
@@ -3388,11 +3391,14 @@
       <c r="D22" s="9" t="s">
         <v>245</v>
       </c>
+      <c r="E22" s="15" t="s">
+        <v>381</v>
+      </c>
       <c r="F22" s="17" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>305</v>
+        <v>380</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>73</v>
@@ -3420,12 +3426,14 @@
       <c r="D23" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="26"/>
+      <c r="E23" s="26" t="s">
+        <v>126</v>
+      </c>
       <c r="F23" s="20" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H23" s="23" t="s">
         <v>77</v>
@@ -3455,13 +3463,13 @@
         <v>261</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H24" s="25" t="s">
         <v>259</v>
@@ -3494,13 +3502,13 @@
         <v>170</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>171</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>209</v>
@@ -3524,10 +3532,10 @@
         <v>78</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>167</v>
@@ -3557,13 +3565,13 @@
         <v>300</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G27" s="15" t="s">
         <v>301</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>299</v>
@@ -3630,10 +3638,10 @@
         <v>78</v>
       </c>
       <c r="F29" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="G29" s="25" t="s">
         <v>358</v>
-      </c>
-      <c r="G29" s="25" t="s">
-        <v>359</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>160</v>
@@ -3665,10 +3673,10 @@
         <v>164</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>163</v>
@@ -3700,7 +3708,7 @@
         <v>175</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>176</v>
@@ -3730,10 +3738,10 @@
         <v>181</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>180</v>
@@ -3768,7 +3776,7 @@
         <v>247</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>184</v>
@@ -3798,10 +3806,10 @@
       </c>
       <c r="E34" s="25"/>
       <c r="F34" s="13" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>188</v>
@@ -3833,16 +3841,16 @@
         <v>126</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>230</v>
@@ -3866,10 +3874,10 @@
         <v>199</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>198</v>
@@ -3898,10 +3906,10 @@
         <v>78</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H37" s="18" t="s">
         <v>195</v>
@@ -3921,60 +3929,60 @@
     </row>
     <row r="38" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="D38" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="B38" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>325</v>
-      </c>
-      <c r="D38" s="13" t="s">
+      <c r="F38" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="G38" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="F38" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="G38" s="15" t="s">
-        <v>329</v>
-      </c>
       <c r="H38" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="I38" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="I38" s="15" t="s">
+      <c r="J38" s="13" t="s">
         <v>323</v>
-      </c>
-      <c r="J38" s="13" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="H39" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>330</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="F39" s="13" t="s">
+      <c r="I39" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="J39" s="13" t="s">
         <v>338</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="H39" s="15" t="s">
-        <v>332</v>
-      </c>
-      <c r="I39" s="15" t="s">
-        <v>333</v>
-      </c>
-      <c r="J39" s="13" t="s">
-        <v>339</v>
       </c>
     </row>
   </sheetData>
